--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-signes-vitaux-document.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-signes-vitaux-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1172,7 +1172,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1195,6 +1195,245 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur de l’observation</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2068,11 +2307,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP75"/>
+  <dimension ref="A1:AP101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.4609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2081,7 +2320,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2096,7 +2335,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -7560,7 +7799,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>94</v>
@@ -7680,32 +7919,28 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>206</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7753,7 +7988,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>209</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7762,50 +7997,50 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>388</v>
+        <v>210</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -7814,20 +8049,18 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>391</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>392</v>
+        <v>213</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7851,43 +8084,43 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>216</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7896,10 +8129,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>398</v>
+        <v>210</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7910,14 +8143,16 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7936,20 +8171,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>384</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7973,13 +8204,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7997,7 +8228,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>399</v>
+        <v>216</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8009,33 +8240,33 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8046,7 +8277,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8058,20 +8289,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>412</v>
+        <v>206</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>413</v>
+        <v>207</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8119,19 +8346,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>411</v>
+        <v>209</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8140,10 +8367,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>210</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8154,10 +8381,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8165,10 +8392,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>391</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8180,17 +8407,15 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8215,77 +8440,79 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>216</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8300,20 +8527,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8337,13 +8560,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8361,19 +8584,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>430</v>
+        <v>216</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8382,10 +8605,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8396,10 +8619,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8422,17 +8645,15 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>440</v>
+        <v>206</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>441</v>
+        <v>207</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8481,7 +8702,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>439</v>
+        <v>209</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8493,33 +8714,33 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>446</v>
+        <v>210</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8530,7 +8751,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8542,17 +8763,15 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>449</v>
+        <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>450</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8589,57 +8808,57 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>216</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>457</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8647,10 +8866,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8662,26 +8881,24 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -8723,19 +8940,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8744,10 +8961,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>136</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8758,10 +8975,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8784,13 +9001,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8799,7 +9016,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>82</v>
@@ -8817,13 +9034,11 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8841,7 +9056,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>209</v>
+        <v>412</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8853,7 +9068,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8865,7 +9080,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8876,21 +9091,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8905,14 +9122,12 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>140</v>
+        <v>415</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8985,7 +9200,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8996,46 +9211,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>207</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9083,19 +9294,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>209</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9107,7 +9318,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9118,10 +9329,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>473</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9132,7 +9343,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9144,13 +9355,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>474</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>475</v>
+        <v>392</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>476</v>
+        <v>393</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9189,31 +9400,31 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>216</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9222,10 +9433,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9236,10 +9447,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>401</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9247,7 +9458,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
@@ -9262,22 +9473,24 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>474</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>481</v>
+        <v>402</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>82</v>
@@ -9319,19 +9532,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>405</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9340,10 +9553,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>483</v>
+        <v>136</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9354,10 +9567,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9383,17 +9596,13 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>485</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9417,13 +9626,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9441,7 +9650,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>412</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9459,13 +9668,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>409</v>
+        <v>136</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9476,21 +9685,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9502,20 +9713,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>494</v>
+        <v>392</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9539,13 +9746,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9563,7 +9770,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>493</v>
+        <v>216</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9575,19 +9782,19 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9598,10 +9805,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>500</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>500</v>
+        <v>397</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9624,18 +9831,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>501</v>
+        <v>206</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>502</v>
+        <v>207</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>503</v>
+        <v>208</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>504</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9683,7 +9888,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>500</v>
+        <v>209</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9695,7 +9900,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9707,7 +9912,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>505</v>
+        <v>210</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9923,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9732,7 +9937,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9744,13 +9949,13 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>507</v>
+        <v>392</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>508</v>
+        <v>393</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9789,31 +9994,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>506</v>
+        <v>216</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9822,10 +10027,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9836,10 +10041,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>510</v>
+        <v>401</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9850,28 +10055,28 @@
         <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>511</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>512</v>
+        <v>402</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>513</v>
+        <v>403</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>514</v>
+        <v>404</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9879,7 +10084,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -9921,19 +10126,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>510</v>
+        <v>405</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -9942,10 +10147,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>516</v>
+        <v>136</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9956,10 +10161,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9970,7 +10175,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -9979,20 +10184,18 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>518</v>
+        <v>426</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>519</v>
+        <v>408</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10041,13 +10244,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>412</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
@@ -10062,10 +10265,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>522</v>
+        <v>136</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10076,10 +10279,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>523</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>523</v>
+        <v>428</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10087,41 +10290,39 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>524</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>524</v>
+        <v>403</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10163,19 +10364,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>523</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10184,10 +10385,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>529</v>
+        <v>136</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10198,10 +10399,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>530</v>
+        <v>430</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>530</v>
+        <v>431</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10212,7 +10413,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10224,13 +10425,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>206</v>
+        <v>432</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>207</v>
+        <v>408</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10281,7 +10482,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>209</v>
+        <v>412</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10293,7 +10494,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10305,7 +10506,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10316,21 +10517,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>433</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>433</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10339,19 +10540,19 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>140</v>
+        <v>434</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>435</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>142</v>
+        <v>436</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10401,19 +10602,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>216</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10425,7 +10626,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10436,46 +10637,44 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>439</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10499,13 +10698,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10523,19 +10722,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10558,10 +10757,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10569,13 +10768,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -10584,20 +10783,18 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>534</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>535</v>
+        <v>448</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10621,13 +10818,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10645,10 +10842,10 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>93</v>
@@ -10663,16 +10860,16 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>297</v>
+        <v>451</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>82</v>
@@ -10680,10 +10877,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>539</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10697,7 +10894,7 @@
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -10706,20 +10903,18 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>381</v>
+        <v>206</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
+        <v>454</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10743,13 +10938,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10767,7 +10962,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>539</v>
+        <v>456</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10776,7 +10971,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -10785,27 +10980,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>388</v>
+        <v>136</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>547</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10816,7 +11011,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>94</v>
@@ -10825,22 +11020,22 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>191</v>
+        <v>458</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>548</v>
+        <v>459</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>549</v>
+        <v>459</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10865,13 +11060,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -10889,7 +11084,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>547</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10898,7 +11093,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10907,41 +11102,41 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>136</v>
+        <v>464</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>398</v>
+        <v>465</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -10953,16 +11148,16 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>401</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>402</v>
+        <v>469</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>404</v>
+        <v>471</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -10990,10 +11185,10 @@
         <v>291</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>405</v>
+        <v>472</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>406</v>
+        <v>473</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11011,16 +11206,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11029,31 +11224,31 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>408</v>
+        <v>136</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>409</v>
+        <v>475</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>553</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>553</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11072,19 +11267,19 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>554</v>
+        <v>478</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>555</v>
+        <v>479</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11109,13 +11304,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11133,7 +11328,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>553</v>
+        <v>476</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11151,23 +11346,3159 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP75">
+  <autoFilter ref="A1:AP101">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11177,7 +14508,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
